--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,9 +780,496 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136865972</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Barlingshultsälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>348612</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6599673</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jens Johansen, Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136865972</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136865966</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Barlingshultsälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>348654</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6599650</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jens Johansen, Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136865966</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136865971</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Barlingshultsälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>348613</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6599582</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stöttes</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jens Johansen, Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136865971</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136865973</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Barlingshultsälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>348536</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6599624</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jens Johansen, Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136865973</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84244354</v>
+        <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>93449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergtjärnen, Vrm</t>
+          <t>Bergtjärnen Barlingshult, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348480</v>
+        <v>348615</v>
       </c>
       <c r="R2" t="n">
-        <v>6599459</v>
+        <v>6599509</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-02-28</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-02-28</t>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,76 +776,77 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ung tallhäll</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/84244354</t>
+          <t>https://artportalen.se/Sighting/136918074</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136865972</v>
+        <v>84244354</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barlingshultsälven, Vrm</t>
+          <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348612</v>
+        <v>348480</v>
       </c>
       <c r="R3" t="n">
-        <v>6599673</v>
+        <v>6599459</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,22 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:36</t>
+          <t>2020-02-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:36</t>
+          <t>2020-02-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,44 +890,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jens Johansen, Jesper Granback</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136865972</t>
+          <t>https://artportalen.se/Sighting/84244354</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136865966</v>
+        <v>136865972</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -927,36 +935,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Barlingshultsälven, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>348654</v>
+        <v>348612</v>
       </c>
       <c r="R4" t="n">
-        <v>6599650</v>
+        <v>6599673</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,54 +1018,70 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136865966</t>
+          <t>https://artportalen.se/Sighting/136865972</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136865971</v>
+        <v>136865966</v>
       </c>
       <c r="B5" t="n">
-        <v>57195</v>
+        <v>58008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Barlingshultsälven, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>348613</v>
+        <v>348654</v>
       </c>
       <c r="R5" t="n">
-        <v>6599582</v>
+        <v>6599650</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,33 +1146,33 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136865971</t>
+          <t>https://artportalen.se/Sighting/136865966</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136865973</v>
+        <v>136918060</v>
       </c>
       <c r="B6" t="n">
-        <v>58164</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1172,26 +1180,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barlingshultsälven, Vrm</t>
+          <t>Bergtjärnen Barlingshult, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>348536</v>
+        <v>348659</v>
       </c>
       <c r="R6" t="n">
-        <v>6599624</v>
+        <v>6599669</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack på tall där ett par av tretå befann sig.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,18 +1256,760 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jens Johansen</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jens Johansen, Jesper Granback</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136918060</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136918075</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergtjärnen Barlingshult, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>348584</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6599541</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack på tall. Jag hörde hack här, högst troligen av tretå som noterades intill, och noterade sedan färska hack där kodan rinner.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918075</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136918076</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergtjärnen Barlingshult, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>348630</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6599623</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Jag hörde hack här, högst troligen av tretå som noterades intill, och noterade sedan färska hack där kodan rinner.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918076</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136865971</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Barlingshultsälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>348613</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6599582</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stöttes</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jens Johansen, Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136865971</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136918056</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergtjärnen Barlingshult, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>348601</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6599687</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918056</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136865973</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Barlingshultsälven, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>348536</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6599624</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jens Johansen, Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136865973</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136918054</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergtjärnen Barlingshult, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>348607</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6599694</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136918054</t>
         </is>
       </c>
     </row>
@@ -1270,6 +2020,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136865972</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>136865966</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136918060</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136918075</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136918076</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136865971</v>
       </c>
       <c r="B9" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136918056</v>
       </c>
       <c r="B10" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136865973</v>
       </c>
       <c r="B11" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>136918054</v>
       </c>
       <c r="B12" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136865972</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>136865966</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136918060</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136918075</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>136918076</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136865971</v>
       </c>
       <c r="B9" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136918056</v>
       </c>
       <c r="B10" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>136865973</v>
       </c>
       <c r="B11" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>136918054</v>
       </c>
       <c r="B12" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -936,11 +936,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Barlingshultsälven, Vrm</t>
@@ -1058,16 +1054,8 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1304,11 +1292,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1444,11 +1428,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1815,11 +1795,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Barlingshultsälven, Vrm</t>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136865972</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136865966</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136918060</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>136918075</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136918076</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136865971</v>
       </c>
       <c r="B9" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>136918056</v>
       </c>
       <c r="B10" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>136865973</v>
       </c>
       <c r="B11" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136918054</v>
       </c>
       <c r="B12" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136865972</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136865966</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136918060</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>136918075</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136918076</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136865971</v>
       </c>
       <c r="B9" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>136918056</v>
       </c>
       <c r="B10" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>136865973</v>
       </c>
       <c r="B11" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136918054</v>
       </c>
       <c r="B12" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>136865972</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136865966</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136918060</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>136918075</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136918076</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>136918056</v>
       </c>
       <c r="B10" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>136865973</v>
       </c>
       <c r="B11" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136918054</v>
       </c>
       <c r="B12" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24601-2025 artfynd.xlsx
+++ b/artfynd/A 24601-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136918074</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
